--- a/ROI.xlsx
+++ b/ROI.xlsx
@@ -8,47 +8,62 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nikhil/Documents/ECS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB00F99-B4E8-6545-B353-041FEB9D7EA8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC786EF6-B56E-7E4E-9ECA-7088BC177E1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Framework_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="2" r:id="rId2"/>
-    <sheet name="Storage_Savings" sheetId="3" r:id="rId3"/>
-    <sheet name="FTE_Savings" sheetId="4" r:id="rId4"/>
-    <sheet name="Executive_Dashboard" sheetId="5" r:id="rId5"/>
+    <sheet name="FY 25 -26" sheetId="6" r:id="rId1"/>
+    <sheet name="Framework_Master" sheetId="1" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="2" r:id="rId3"/>
+    <sheet name="Storage_Savings" sheetId="3" r:id="rId4"/>
+    <sheet name="FTE_Savings" sheetId="4" r:id="rId5"/>
+    <sheet name="Executive_Dashboard" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">Executive_Dashboard!$A$2:$A$8</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Executive_Dashboard!$B$1</definedName>
-    <definedName name="_xlchart.v2.10" hidden="1">Executive_Dashboard!$F$2:$F$8</definedName>
-    <definedName name="_xlchart.v2.11" hidden="1">Executive_Dashboard!$A$2</definedName>
-    <definedName name="_xlchart.v2.12" hidden="1">Executive_Dashboard!$A$3</definedName>
-    <definedName name="_xlchart.v2.13" hidden="1">Executive_Dashboard!$A$4</definedName>
-    <definedName name="_xlchart.v2.14" hidden="1">Executive_Dashboard!$A$5</definedName>
-    <definedName name="_xlchart.v2.15" hidden="1">Executive_Dashboard!$A$6</definedName>
-    <definedName name="_xlchart.v2.16" hidden="1">Executive_Dashboard!$A$7</definedName>
-    <definedName name="_xlchart.v2.17" hidden="1">Executive_Dashboard!$A$8</definedName>
-    <definedName name="_xlchart.v2.18" hidden="1">Executive_Dashboard!$B$1:$F$1</definedName>
-    <definedName name="_xlchart.v2.19" hidden="1">Executive_Dashboard!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Executive_Dashboard!$B$2:$B$8</definedName>
-    <definedName name="_xlchart.v2.20" hidden="1">Executive_Dashboard!$B$3:$F$3</definedName>
-    <definedName name="_xlchart.v2.21" hidden="1">Executive_Dashboard!$B$4:$F$4</definedName>
-    <definedName name="_xlchart.v2.22" hidden="1">Executive_Dashboard!$B$5:$F$5</definedName>
-    <definedName name="_xlchart.v2.23" hidden="1">Executive_Dashboard!$B$6:$F$6</definedName>
-    <definedName name="_xlchart.v2.24" hidden="1">Executive_Dashboard!$B$7:$F$7</definedName>
-    <definedName name="_xlchart.v2.25" hidden="1">Executive_Dashboard!$B$8:$F$8</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Executive_Dashboard!$C$1</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">Executive_Dashboard!$C$2:$C$8</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">Executive_Dashboard!$D$1</definedName>
-    <definedName name="_xlchart.v2.6" hidden="1">Executive_Dashboard!$D$2:$D$8</definedName>
-    <definedName name="_xlchart.v2.7" hidden="1">Executive_Dashboard!$E$1</definedName>
-    <definedName name="_xlchart.v2.8" hidden="1">Executive_Dashboard!$E$2:$E$8</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">Executive_Dashboard!$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FY 25 -26'!$A$1:$L$18</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Executive_Dashboard!$A$2</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Executive_Dashboard!$A$3</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Executive_Dashboard!$A$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Executive_Dashboard!$A$3</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Executive_Dashboard!$A$4</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Executive_Dashboard!$A$4</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Executive_Dashboard!$A$5</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Executive_Dashboard!$A$2</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Executive_Dashboard!$A$3</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Executive_Dashboard!$A$4</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Executive_Dashboard!$A$5</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Executive_Dashboard!$A$5</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
+    <definedName name="_xlchart.v2.10" hidden="1">Executive_Dashboard!$A$3</definedName>
+    <definedName name="_xlchart.v2.11" hidden="1">Executive_Dashboard!$A$4</definedName>
+    <definedName name="_xlchart.v2.12" hidden="1">Executive_Dashboard!$A$5</definedName>
+    <definedName name="_xlchart.v2.13" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
+    <definedName name="_xlchart.v2.14" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
+    <definedName name="_xlchart.v2.15" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
+    <definedName name="_xlchart.v2.16" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
+    <definedName name="_xlchart.v2.17" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
+    <definedName name="_xlchart.v2.9" hidden="1">Executive_Dashboard!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -60,11 +75,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
   <si>
     <t>Framework</t>
   </si>
   <si>
+    <t xml:space="preserve">Application </t>
+  </si>
+  <si>
+    <t>Total Obs</t>
+  </si>
+  <si>
+    <t>Emails/Observation</t>
+  </si>
+  <si>
+    <t>Emails without ECS</t>
+  </si>
+  <si>
+    <t>Emails Saved</t>
+  </si>
+  <si>
+    <t>Minutes/Email</t>
+  </si>
+  <si>
+    <t>Hours Saved</t>
+  </si>
+  <si>
+    <t>Cost/Hour (Rs)</t>
+  </si>
+  <si>
+    <t>Annual Saving (Cr)</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>VAPT</t>
+  </si>
+  <si>
+    <t>PCI DSS</t>
+  </si>
+  <si>
+    <t>DPSC</t>
+  </si>
+  <si>
+    <t>CSITE</t>
+  </si>
+  <si>
+    <t>ITPP</t>
+  </si>
+  <si>
+    <t>ITDRM</t>
+  </si>
+  <si>
+    <t>MBSS</t>
+  </si>
+  <si>
+    <t>ASST</t>
+  </si>
+  <si>
+    <t>IS Audit</t>
+  </si>
+  <si>
+    <t>Internal Audit</t>
+  </si>
+  <si>
+    <t>TPRE</t>
+  </si>
+  <si>
+    <t>TPRM</t>
+  </si>
+  <si>
+    <t>Prisma Alerts</t>
+  </si>
+  <si>
+    <t>Cloud Security Reviews</t>
+  </si>
+  <si>
+    <t>OS Baselining</t>
+  </si>
+  <si>
+    <t>DB Baselining</t>
+  </si>
+  <si>
+    <t>Middleware Baselining</t>
+  </si>
+  <si>
     <t>Applications</t>
   </si>
   <si>
@@ -74,129 +170,63 @@
     <t>Total Observations</t>
   </si>
   <si>
-    <t>Emails/Observation</t>
-  </si>
-  <si>
-    <t>Emails Saved</t>
-  </si>
-  <si>
-    <t>Minutes/Email</t>
-  </si>
-  <si>
-    <t>Hours Saved</t>
-  </si>
-  <si>
-    <t>Cost/Hour (Rs)</t>
-  </si>
-  <si>
-    <t>Annual Saving (Cr)</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>VAPT</t>
+    <t>Emails w/o ECS</t>
   </si>
   <si>
     <t>37500 observations x 8 emails</t>
   </si>
   <si>
-    <t>PCI DSS</t>
-  </si>
-  <si>
     <t>Evidence reuse across controls</t>
   </si>
   <si>
-    <t>DPSC</t>
-  </si>
-  <si>
     <t>Compliance evidence automation</t>
   </si>
   <si>
-    <t>CSITE</t>
-  </si>
-  <si>
     <t>Cyber examination evidence automation</t>
   </si>
   <si>
-    <t>ITPP</t>
-  </si>
-  <si>
     <t>Policy compliance evidence automation</t>
   </si>
   <si>
-    <t>ITDRM</t>
-  </si>
-  <si>
     <t>Digital risk review automation</t>
   </si>
   <si>
-    <t>MBSS</t>
-  </si>
-  <si>
     <t>Mobile Banking Security Standard</t>
   </si>
   <si>
-    <t>ASST</t>
-  </si>
-  <si>
     <t>Application Security Standard</t>
   </si>
   <si>
-    <t>IS Audit</t>
-  </si>
-  <si>
     <t>IS audit evidence handling</t>
   </si>
   <si>
-    <t>Internal Audit</t>
-  </si>
-  <si>
     <t>Audit evidence reuse</t>
   </si>
   <si>
-    <t>TPRE</t>
-  </si>
-  <si>
     <t>Third-party assessment evidence</t>
   </si>
   <si>
-    <t>TPRM</t>
-  </si>
-  <si>
     <t>Vendor risk evidence management</t>
   </si>
   <si>
-    <t>Prisma Alerts</t>
-  </si>
-  <si>
     <t>Cloud alert evidence tracking</t>
   </si>
   <si>
-    <t>Cloud Security Reviews</t>
-  </si>
-  <si>
     <t>Cloud compliance reviews</t>
   </si>
   <si>
-    <t>OS Baselining</t>
-  </si>
-  <si>
     <t>OS baseline validation</t>
   </si>
   <si>
-    <t>DB Baselining</t>
-  </si>
-  <si>
     <t>Database baseline validation</t>
   </si>
   <si>
-    <t>Middleware Baselining</t>
-  </si>
-  <si>
     <t>Middleware baseline validation</t>
   </si>
   <si>
+    <t xml:space="preserve">Annual Saving </t>
+  </si>
+  <si>
     <t>Rounded Total</t>
   </si>
   <si>
@@ -206,9 +236,6 @@
     <t>Annual Savings (Cr)</t>
   </si>
   <si>
-    <t>3-Year Cumulative Savings (Cr)</t>
-  </si>
-  <si>
     <t>Year 1</t>
   </si>
   <si>
@@ -296,6 +323,9 @@
     <t>₹20L salary / 2000 hours</t>
   </si>
   <si>
+    <t>Rounded executive number (90k*1000)</t>
+  </si>
+  <si>
     <t>Average Salary (Rs)</t>
   </si>
   <si>
@@ -305,65 +335,42 @@
     <t>FTE Equivalent</t>
   </si>
   <si>
-    <t>90000/2000</t>
-  </si>
-  <si>
-    <t>Cumulative Savings (Cr)</t>
+    <t>45438/2000</t>
   </si>
   <si>
     <t>ECS Cost (Cr)</t>
   </si>
   <si>
-    <t>Cumulative Cost (Cr)</t>
-  </si>
-  <si>
     <t>Net Benefit (Cr)</t>
   </si>
   <si>
-    <t>Payback Status</t>
-  </si>
-  <si>
-    <t>Achieved</t>
-  </si>
-  <si>
-    <t>9cr annual savings for 9000 hrs.</t>
-  </si>
-  <si>
-    <t>Rounded executive number (90k*1000)</t>
+    <t>Year 4</t>
   </si>
   <si>
     <t>Year 5</t>
   </si>
   <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <t>REMARKS</t>
-  </si>
-  <si>
-    <t>50 APPS ONBARDED EVERY YEAR</t>
-  </si>
-  <si>
-    <t>SAVINGS OF 9CR PER 50 APPS</t>
-  </si>
-  <si>
-    <t>CUMMMULATIVE SAVING INCREASING BY 18CR PER 100 APPS EVERY YEARS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COST IS 2.2 OPEX EVERY YEAR CONSTANT </t>
-  </si>
-  <si>
-    <t>CUULATIVE COSTINCREASING BY 2.2 CR PER YEAR</t>
-  </si>
-  <si>
-    <t>NET BENEFT IS  INCREASING EVERY YEAR</t>
+    <t>Year 6</t>
+  </si>
+  <si>
+    <t>Year 7</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>Emails</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="[$INR]\ #,##0"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,16 +401,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -411,11 +447,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -424,8 +487,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -518,9 +607,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
+              <c:f>Executive_Dashboard!$B$1:$H$1</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Year 1</c:v>
                 </c:pt>
@@ -535,18 +624,24 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Year 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Year 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Year 7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Executive_Dashboard!$B$2:$F$2</c:f>
+              <c:f>Executive_Dashboard!$B$2:$H$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>100</c:v>
@@ -555,17 +650,23 @@
                   <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>300</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7AD2-4B47-9B9A-949D0DF115D0}"/>
+              <c16:uniqueId val="{00000000-EE2B-464F-913D-921963A55B38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -595,9 +696,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
+              <c:f>Executive_Dashboard!$B$1:$H$1</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Year 1</c:v>
                 </c:pt>
@@ -612,37 +713,49 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Year 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Year 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Year 7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Executive_Dashboard!$B$3:$F$3</c:f>
+              <c:f>Executive_Dashboard!$B$3:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>4.54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>18.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>36.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>72.64</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>90.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>72.64</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>145.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7AD2-4B47-9B9A-949D0DF115D0}"/>
+              <c16:uniqueId val="{00000001-EE2B-464F-913D-921963A55B38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -655,7 +768,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Cumulative Savings (Cr)</c:v>
+                  <c:v>ECS Cost (Cr)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -672,9 +785,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
+              <c:f>Executive_Dashboard!$B$1:$H$1</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Year 1</c:v>
                 </c:pt>
@@ -689,37 +802,49 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Year 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Year 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Year 7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Executive_Dashboard!$B$4:$F$4</c:f>
+              <c:f>Executive_Dashboard!$B$4:$H$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>2.2000000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108</c:v>
+                  <c:v>2.2000000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>162</c:v>
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2000000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7AD2-4B47-9B9A-949D0DF115D0}"/>
+              <c16:uniqueId val="{00000002-EE2B-464F-913D-921963A55B38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -732,7 +857,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ECS Cost (Cr)</c:v>
+                  <c:v>Net Benefit (Cr)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -749,9 +874,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
+              <c:f>Executive_Dashboard!$B$1:$H$1</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Year 1</c:v>
                 </c:pt>
@@ -766,191 +891,49 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Year 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Year 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Year 7</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Executive_Dashboard!$B$5:$F$5</c:f>
+              <c:f>Executive_Dashboard!$B$5:$H$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>16.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>34.119999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>70.44</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>88.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70.44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>143.08000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7AD2-4B47-9B9A-949D0DF115D0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Executive_Dashboard!$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cumulative Cost (Cr)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Year 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Year 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Year 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Year 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Year 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Executive_Dashboard!$B$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>12.599999999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7AD2-4B47-9B9A-949D0DF115D0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Executive_Dashboard!$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Net Benefit (Cr)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Executive_Dashboard!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Year 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Year 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Year 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Year 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Year 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Executive_Dashboard!$B$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>54.8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>97.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>149.4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-7AD2-4B47-9B9A-949D0DF115D0}"/>
+              <c16:uniqueId val="{00000003-EE2B-464F-913D-921963A55B38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -964,108 +947,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="821639792"/>
-        <c:axId val="821696496"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredBarSeries>
-              <c15:ser>
-                <c:idx val="6"/>
-                <c:order val="6"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Executive_Dashboard!$A$8</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Payback Status</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:solidFill>
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="60000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:invertIfNegative val="0"/>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Executive_Dashboard!$B$1:$F$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="5"/>
-                      <c:pt idx="0">
-                        <c:v>Year 1</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>Year 2</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>Year 3</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>Year 4</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>Year 5</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Executive_Dashboard!$B$8:$F$8</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
-                      <c:pt idx="0">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>0</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000006-7AD2-4B47-9B9A-949D0DF115D0}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredBarSeries>
-          </c:ext>
-        </c:extLst>
+        <c:axId val="820969952"/>
+        <c:axId val="820971584"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="821639792"/>
+        <c:axId val="820969952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1108,7 +994,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="821696496"/>
+        <c:crossAx val="820971584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1116,7 +1002,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="821696496"/>
+        <c:axId val="820971584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1167,7 +1053,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="821639792"/>
+        <c:crossAx val="820969952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1795,22 +1681,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>273050</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>254000</xdr:rowOff>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7404100</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD2496CF-D3B5-3940-BD4D-17ABCAC8947D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A002972-B555-EC4E-96D2-5C66C770F4FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2115,771 +2001,1649 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-    <col min="6" max="8" width="15" customWidth="1"/>
-    <col min="9" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="60" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93164FE1-3E78-4F24-847C-5FF9BDB7067B}">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="23" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="21">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="19" customFormat="1" ht="44">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" ht="21">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
+        <v>600</v>
+      </c>
+      <c r="C2" s="5">
         <v>25</v>
       </c>
-      <c r="C2" s="2">
-        <v>1500</v>
-      </c>
-      <c r="D2" s="2">
-        <v>37500</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="7">
+        <v>14000</v>
+      </c>
+      <c r="E2" s="7">
         <v>8</v>
       </c>
-      <c r="F2" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2">
-        <v>16667</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="F2" s="7">
+        <f>D2*E2</f>
+        <v>112000</v>
+      </c>
+      <c r="G2" s="7">
+        <f>F2*0.6</f>
+        <v>67200</v>
+      </c>
+      <c r="H2" s="7">
+        <v>5</v>
+      </c>
+      <c r="I2" s="7">
+        <f>G2*H2/60</f>
+        <v>5600</v>
+      </c>
+      <c r="J2" s="7">
         <v>1000</v>
       </c>
-      <c r="J2" s="2">
-        <v>1.67</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="7">
+        <f>I2*J2/10000000</f>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="21">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="21">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="7">
+        <v>98</v>
+      </c>
+      <c r="C3" s="7">
+        <v>22</v>
+      </c>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D18" si="0">B3*C3</f>
+        <v>2156</v>
+      </c>
+      <c r="E3" s="7">
+        <v>6</v>
+      </c>
+      <c r="F3" s="7">
+        <f>D3*E3</f>
+        <v>12936</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" ref="G3:G18" si="1">F3*0.6</f>
+        <v>7761.5999999999995</v>
+      </c>
+      <c r="H3" s="7">
+        <v>5</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I18" si="2">G3*H3/60</f>
+        <v>646.79999999999995</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K18" si="3">I3*J3/10000000</f>
+        <v>6.4680000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="7">
+        <v>58</v>
+      </c>
+      <c r="C4" s="7">
+        <v>122</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" si="0"/>
+        <v>7076</v>
+      </c>
+      <c r="E4" s="7">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F18" si="4">D4*E4</f>
+        <v>42456</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="1"/>
+        <v>25473.599999999999</v>
+      </c>
+      <c r="H4" s="7">
+        <v>5</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="2"/>
+        <v>2122.8000000000002</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="3"/>
+        <v>0.21228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="21">
+      <c r="A5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7">
+        <v>600</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="4"/>
+        <v>18000</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="1"/>
+        <v>10800</v>
+      </c>
+      <c r="H5" s="7">
+        <v>5</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="3"/>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7">
+        <v>902</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" si="0"/>
+        <v>90200</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="4"/>
+        <v>451000</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="1"/>
+        <v>270600</v>
+      </c>
+      <c r="H6" s="7">
+        <v>5</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="2"/>
+        <v>22550</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="3"/>
+        <v>2.2549999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7">
+        <v>900</v>
+      </c>
+      <c r="C7" s="7">
+        <v>52</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="0"/>
+        <v>46800</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="4"/>
+        <v>234000</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="1"/>
+        <v>140400</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="2"/>
+        <v>11700</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="3"/>
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="21">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7">
+        <v>600</v>
+      </c>
+      <c r="C8" s="7">
+        <v>40</v>
+      </c>
+      <c r="D8" s="5">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>120000</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>900</v>
+      </c>
+      <c r="C9" s="7">
+        <v>149</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="0"/>
+        <v>134100</v>
+      </c>
+      <c r="E9" s="7">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="4"/>
+        <v>670500</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="1"/>
+        <v>402300</v>
+      </c>
+      <c r="H9" s="7">
+        <v>5</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="2"/>
+        <v>33525</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="3"/>
+        <v>3.3525</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21">
+      <c r="A10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>900</v>
+      </c>
+      <c r="C10" s="7">
+        <v>100</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" si="0"/>
+        <v>90000</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="4"/>
+        <v>540000</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>324000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="2"/>
+        <v>27000</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="3"/>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7">
+        <v>162</v>
+      </c>
+      <c r="C11" s="17">
+        <f>D11/B11</f>
+        <v>3.8765432098765431</v>
+      </c>
+      <c r="D11" s="5">
+        <v>628</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="4"/>
+        <v>3140</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>1884</v>
+      </c>
+      <c r="H11" s="7">
+        <v>5</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="3"/>
+        <v>1.5699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>300</v>
+      </c>
+      <c r="C12" s="7">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="4"/>
+        <v>15000</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>5</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="J12" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="3"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7">
+        <v>300</v>
+      </c>
+      <c r="C13" s="7">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="4"/>
+        <v>15000</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>5</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="J13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="3"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="21">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7">
+        <v>600</v>
+      </c>
+      <c r="C14" s="7">
+        <v>20</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="4"/>
+        <v>60000</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="1"/>
+        <v>36000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>5</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="J14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="21">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="7">
+        <v>600</v>
+      </c>
+      <c r="C15" s="7">
+        <v>20</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="E15" s="7">
+        <v>5</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="4"/>
+        <v>60000</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="1"/>
+        <v>36000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>5</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="J15" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="21">
+      <c r="A16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2">
-        <v>500</v>
-      </c>
-      <c r="D3" s="2">
-        <v>12500</v>
-      </c>
-      <c r="E3" s="2">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2">
-        <v>96000</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>8000</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="B16" s="7">
+        <v>827</v>
+      </c>
+      <c r="C16" s="7">
+        <v>150</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="0"/>
+        <v>124050</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="4"/>
+        <v>496200</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="1"/>
+        <v>297720</v>
+      </c>
+      <c r="H16" s="7">
+        <v>5</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="2"/>
+        <v>24810</v>
+      </c>
+      <c r="J16" s="7">
         <v>1000</v>
       </c>
-      <c r="J3" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2">
-        <v>450</v>
-      </c>
-      <c r="D4" s="2">
-        <v>11250</v>
-      </c>
-      <c r="E4" s="2">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2">
-        <v>84000</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>7000</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="K16" s="7">
+        <f t="shared" si="3"/>
+        <v>2.4809999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="21">
+      <c r="A17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="7">
+        <v>486</v>
+      </c>
+      <c r="C17" s="7">
+        <v>150</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="0"/>
+        <v>72900</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="4"/>
+        <v>291600</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="1"/>
+        <v>174960</v>
+      </c>
+      <c r="H17" s="7">
+        <v>5</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="2"/>
+        <v>14580</v>
+      </c>
+      <c r="J17" s="7">
         <v>1000</v>
       </c>
-      <c r="J4" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="21">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2">
-        <v>400</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="E5" s="2">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2">
-        <v>72000</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="K17" s="7">
+        <f t="shared" si="3"/>
+        <v>1.458</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="21">
+      <c r="A18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="7">
+        <v>521</v>
+      </c>
+      <c r="C18" s="7">
+        <v>150</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="0"/>
+        <v>78150</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="4"/>
+        <v>312600</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="1"/>
+        <v>187560</v>
+      </c>
+      <c r="H18" s="7">
+        <v>5</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="2"/>
+        <v>15630</v>
+      </c>
+      <c r="J18" s="7">
         <v>1000</v>
       </c>
-      <c r="J5" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="21">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2">
-        <v>250</v>
-      </c>
-      <c r="D6" s="2">
-        <v>6250</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2">
-        <v>4000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="21">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2">
-        <v>250</v>
-      </c>
-      <c r="D7" s="2">
-        <v>6250</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G7" s="2">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2">
-        <v>4000</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="21">
-      <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="2">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2">
-        <v>300</v>
-      </c>
-      <c r="D8" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2">
-        <v>350</v>
-      </c>
-      <c r="D9" s="2">
-        <v>8750</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2">
-        <v>72000</v>
-      </c>
-      <c r="G9" s="2">
-        <v>5</v>
-      </c>
-      <c r="H9" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2">
-        <v>400</v>
-      </c>
-      <c r="D10" s="2">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="2">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2">
-        <v>72000</v>
-      </c>
-      <c r="G10" s="2">
-        <v>5</v>
-      </c>
-      <c r="H10" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="21">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2">
-        <v>350</v>
-      </c>
-      <c r="D11" s="2">
-        <v>8750</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5</v>
-      </c>
-      <c r="F11" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G11" s="2">
-        <v>5</v>
-      </c>
-      <c r="H11" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="21">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>200</v>
-      </c>
-      <c r="D12" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E12" s="2">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2">
-        <v>36000</v>
-      </c>
-      <c r="G12" s="2">
-        <v>5</v>
-      </c>
-      <c r="H12" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="21">
-      <c r="A13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="2">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2">
-        <v>200</v>
-      </c>
-      <c r="D13" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E13" s="2">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2">
-        <v>36000</v>
-      </c>
-      <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="21">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2">
-        <v>300</v>
-      </c>
-      <c r="D14" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E14" s="2">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G14" s="2">
-        <v>5</v>
-      </c>
-      <c r="H14" s="2">
-        <v>4000</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="2">
-        <v>25</v>
-      </c>
-      <c r="C15" s="2">
-        <v>250</v>
-      </c>
-      <c r="D15" s="2">
-        <v>6250</v>
-      </c>
-      <c r="E15" s="2">
-        <v>5</v>
-      </c>
-      <c r="F15" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G15" s="2">
-        <v>5</v>
-      </c>
-      <c r="H15" s="2">
-        <v>4000</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="21">
-      <c r="A16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="2">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2">
-        <v>150</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3750</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2">
-        <v>36000</v>
-      </c>
-      <c r="G16" s="2">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="21">
-      <c r="A17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="2">
-        <v>25</v>
-      </c>
-      <c r="C17" s="2">
-        <v>125</v>
-      </c>
-      <c r="D17" s="2">
-        <v>3125</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2">
-        <v>30000</v>
-      </c>
-      <c r="G17" s="2">
-        <v>5</v>
-      </c>
-      <c r="H17" s="2">
-        <v>2500</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="21">
-      <c r="A18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2">
-        <v>25</v>
-      </c>
-      <c r="C18" s="2">
-        <v>125</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3125</v>
-      </c>
-      <c r="E18" s="2">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2">
-        <v>30000</v>
-      </c>
-      <c r="G18" s="2">
-        <v>5</v>
-      </c>
-      <c r="H18" s="2">
-        <v>2500</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="3"/>
+        <v>1.5629999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="21">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="21">
-      <c r="H20" s="5">
-        <f>SUM(H2:H18)</f>
-        <v>89667</v>
-      </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5">
-        <f>SUM(J2:J18)</f>
-        <v>8.9700000000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="21">
-      <c r="A21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="3">
-        <v>90000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>9</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>88</v>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="20">
+        <f>SUM(K2:K19)</f>
+        <v>17.27216</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:L18" xr:uid="{68C4DC9B-C7EB-4E9D-BC32-606066ADB7FB}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="21">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1500</v>
+      </c>
+      <c r="D2" s="2">
+        <v>37500</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <f>E2*D2</f>
+        <v>300000</v>
+      </c>
+      <c r="G2" s="2">
+        <f>F2*0.6</f>
+        <v>180000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2">
+        <f>H2*G2/60</f>
+        <v>15000</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K2" s="10">
+        <f>I2*J2/10000000</f>
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="21">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>500</v>
+      </c>
+      <c r="D3" s="2">
+        <v>12500</v>
+      </c>
+      <c r="E3" s="2">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F18" si="0">E3*D3</f>
+        <v>75000</v>
+      </c>
+      <c r="G3" s="2">
+        <f>F3*0.6</f>
+        <v>45000</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I18" si="1">H3*G3/60</f>
+        <v>3750</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K18" si="2">I3*J3/10000000</f>
+        <v>0.375</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2">
+        <v>450</v>
+      </c>
+      <c r="D4" s="2">
+        <v>11250</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>67500</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" ref="G4:G18" si="3">F4*0.6</f>
+        <v>40500</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="1"/>
+        <v>3375</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="2"/>
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="21">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2">
+        <v>400</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>60000</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="3"/>
+        <v>36000</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2">
+        <v>250</v>
+      </c>
+      <c r="D6" s="2">
+        <v>6250</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>31250</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="3"/>
+        <v>18750</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="1"/>
+        <v>1562.5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="2"/>
+        <v>0.15625</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2">
+        <v>500</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6250</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>31250</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="3"/>
+        <v>18750</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="11">
+        <f t="shared" si="1"/>
+        <v>1562.5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="2"/>
+        <v>0.15625</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="21">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2">
+        <v>300</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>37500</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="3"/>
+        <v>22500</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" si="1"/>
+        <v>1875</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.1875</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>350</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8750</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>43750</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="3"/>
+        <v>26250</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" si="1"/>
+        <v>2187.5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="2"/>
+        <v>0.21875</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2">
+        <v>400</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>60000</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="3"/>
+        <v>36000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>350</v>
+      </c>
+      <c r="D11" s="2">
+        <v>8750</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>43750</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="3"/>
+        <v>26250</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="11">
+        <f t="shared" si="1"/>
+        <v>2187.5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="2"/>
+        <v>0.21875</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>200</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+      <c r="H12" s="2">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2">
+        <v>200</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="2">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="21">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2">
+        <v>300</v>
+      </c>
+      <c r="D14" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>37500</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="3"/>
+        <v>22500</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="1"/>
+        <v>1875</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="2"/>
+        <v>0.1875</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="21">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2">
+        <v>250</v>
+      </c>
+      <c r="D15" s="2">
+        <v>6250</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>31250</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="3"/>
+        <v>18750</v>
+      </c>
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
+      <c r="I15" s="11">
+        <f t="shared" si="1"/>
+        <v>1562.5</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="2"/>
+        <v>0.15625</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="21">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2">
+        <v>150</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3750</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="3"/>
+        <v>9000</v>
+      </c>
+      <c r="H16" s="2">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="17" spans="1:12" ht="21">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2">
+        <v>125</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3125</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>12500</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="3"/>
+        <v>7500</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="1"/>
+        <v>625</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="2"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="3" t="s">
+    </row>
+    <row r="18" spans="1:12" ht="21">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2">
+        <v>125</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3125</v>
+      </c>
+      <c r="E18" s="2">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="0"/>
+        <v>12500</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="3"/>
+        <v>7500</v>
+      </c>
+      <c r="H18" s="2">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="1"/>
+        <v>625</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="2"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="21">
-      <c r="A2" s="2" t="s">
+    <row r="19" spans="1:12" ht="15" customHeight="1">
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" ht="21">
+      <c r="I20" s="12">
+        <f>SUM(I2:I18)</f>
+        <v>45437.5</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="13">
+        <f>SUM(K2:K19)</f>
+        <v>4.5437500000000002</v>
+      </c>
+      <c r="L20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="2">
+    </row>
+    <row r="21" spans="1:12" ht="21">
+      <c r="A21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="21">
-      <c r="A3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="2">
-        <v>100</v>
-      </c>
-      <c r="C3" s="2">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="21">
-      <c r="A4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="2">
-        <v>200</v>
-      </c>
-      <c r="C4" s="2">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2">
-        <v>63</v>
-      </c>
+      <c r="I21" s="3"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21">
+      <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2">
+        <f>C2+C2</f>
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="21">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2">
+        <f>C3+C2</f>
+        <v>13.620000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21">
+      <c r="A5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>9</v>
@@ -2890,87 +3654,87 @@
     </row>
     <row r="2" spans="1:5" ht="21">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2">
         <v>0.15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D3" s="2">
         <v>0.05</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2">
         <v>0.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="21">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2">
         <v>0.15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="21">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2">
         <v>0.1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="21">
@@ -2981,25 +3745,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>10</v>
@@ -3009,22 +3777,22 @@
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
-        <v>90000</v>
+      <c r="B2" s="11">
+        <v>45437.5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1000</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21">
@@ -3032,78 +3800,84 @@
         <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>9</v>
+        <v>4.54</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" s="2">
         <v>2000000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B6" s="2">
-        <v>45</v>
+        <v>22.72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="103.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="H1" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -3112,161 +3886,383 @@
         <v>200</v>
       </c>
       <c r="E2" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2">
+        <v>500</v>
+      </c>
+      <c r="G2" s="2">
         <v>400</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>93</v>
+      <c r="H2" s="2">
+        <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="21">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>9</v>
+        <v>4.54</v>
       </c>
       <c r="C3" s="2">
-        <v>18</v>
+        <f>B3*4</f>
+        <v>18.16</v>
       </c>
       <c r="D3" s="2">
-        <v>36</v>
+        <f>B3*8</f>
+        <v>36.32</v>
       </c>
       <c r="E3" s="2">
-        <v>45</v>
+        <f>D3*2</f>
+        <v>72.64</v>
       </c>
       <c r="F3" s="2">
-        <v>54</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>94</v>
+        <f>C3*5</f>
+        <v>90.8</v>
+      </c>
+      <c r="G3" s="2">
+        <f>C3*4</f>
+        <v>72.64</v>
+      </c>
+      <c r="H3" s="2">
+        <f>C3*8</f>
+        <v>145.28</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2">
-        <f>C3+B4</f>
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>D3+C4</f>
-        <v>63</v>
-      </c>
-      <c r="E4" s="5">
-        <f>E3+D4</f>
-        <v>108</v>
-      </c>
-      <c r="F4" s="5">
-        <f>F3+E4</f>
-        <v>162</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21">
       <c r="A5" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B5" s="2">
-        <v>4</v>
+        <f>B3-B4</f>
+        <v>0.54</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <f t="shared" ref="C5:D5" si="0">C3-C4</f>
+        <v>16.16</v>
       </c>
       <c r="D5" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F5" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="2" t="s">
-        <v>96</v>
+        <f t="shared" si="0"/>
+        <v>34.119999999999997</v>
+      </c>
+      <c r="E5" s="2">
+        <f>E3-E4</f>
+        <v>70.44</v>
+      </c>
+      <c r="F5" s="2">
+        <f>F3-F4</f>
+        <v>88.6</v>
+      </c>
+      <c r="G5" s="2">
+        <f>G3-G4</f>
+        <v>70.44</v>
+      </c>
+      <c r="H5" s="2">
+        <f>H3-H4</f>
+        <v>143.08000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21">
-      <c r="A6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="2">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
-        <f>B6+C5</f>
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
-        <f>C6+D5</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E6" s="5">
-        <f>D6+E5</f>
-        <v>10.399999999999999</v>
-      </c>
-      <c r="F6" s="5">
-        <f>E6+F5</f>
-        <v>12.599999999999998</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="21">
-      <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <f>C4-C6</f>
-        <v>21</v>
-      </c>
-      <c r="D7" s="2">
-        <f>D4-D6</f>
-        <v>54.8</v>
-      </c>
-      <c r="E7" s="5">
-        <f>E4-E6</f>
-        <v>97.6</v>
-      </c>
-      <c r="F7" s="5">
-        <f>F4-F6</f>
-        <v>149.4</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="21">
-      <c r="A8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="21">
+      <c r="A9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K0000FF Classification - Internal</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f9ef682c-7912-4780-84f4-a971df966cba" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b405d1f-d10b-4093-82f9-1855360715f6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEC45E153F28EE4787994493462BB723" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cc717bbd999d588741822980c3ad8145">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b405d1f-d10b-4093-82f9-1855360715f6" xmlns:ns3="f9ef682c-7912-4780-84f4-a971df966cba" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb756d61f9318ee21e8beb465d11a9eb" ns2:_="" ns3:_="">
+    <xsd:import namespace="7b405d1f-d10b-4093-82f9-1855360715f6"/>
+    <xsd:import namespace="f9ef682c-7912-4780-84f4-a971df966cba"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7b405d1f-d10b-4093-82f9-1855360715f6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0a82e066-c8c7-45b9-bb03-520ac438c964" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f9ef682c-7912-4780-84f4-a971df966cba" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c0d53ece-7e7d-4303-a71c-9444a71c63d4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f9ef682c-7912-4780-84f4-a971df966cba">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0D1079-5B4B-49D4-ADDA-486E009CBEBA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9ef682c-7912-4780-84f4-a971df966cba"/>
+    <ds:schemaRef ds:uri="7b405d1f-d10b-4093-82f9-1855360715f6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D08681-8533-4464-BCEB-02BE874F812E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7b405d1f-d10b-4093-82f9-1855360715f6"/>
+    <ds:schemaRef ds:uri="f9ef682c-7912-4780-84f4-a971df966cba"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20FF6A95-94CC-4354-9C77-CD818EDE354A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ROI.xlsx
+++ b/ROI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nikhil/Documents/ECS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC786EF6-B56E-7E4E-9ECA-7088BC177E1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1B385D-2B1F-404D-9EA2-77193F829CA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FY 25 -26" sheetId="6" r:id="rId1"/>
@@ -22,42 +22,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FY 25 -26'!$A$1:$L$18</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Executive_Dashboard!$A$2</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Executive_Dashboard!$A$3</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Executive_Dashboard!$A$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Executive_Dashboard!$A$3</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Executive_Dashboard!$A$4</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Executive_Dashboard!$A$4</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Executive_Dashboard!$A$5</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Executive_Dashboard!$A$2</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Executive_Dashboard!$A$3</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Executive_Dashboard!$A$4</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Executive_Dashboard!$A$5</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Executive_Dashboard!$A$5</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
-    <definedName name="_xlchart.v2.10" hidden="1">Executive_Dashboard!$A$3</definedName>
-    <definedName name="_xlchart.v2.11" hidden="1">Executive_Dashboard!$A$4</definedName>
-    <definedName name="_xlchart.v2.12" hidden="1">Executive_Dashboard!$A$5</definedName>
-    <definedName name="_xlchart.v2.13" hidden="1">Executive_Dashboard!$B$1:$H$1</definedName>
-    <definedName name="_xlchart.v2.14" hidden="1">Executive_Dashboard!$B$2:$H$2</definedName>
-    <definedName name="_xlchart.v2.15" hidden="1">Executive_Dashboard!$B$3:$H$3</definedName>
-    <definedName name="_xlchart.v2.16" hidden="1">Executive_Dashboard!$B$4:$H$4</definedName>
-    <definedName name="_xlchart.v2.17" hidden="1">Executive_Dashboard!$B$5:$H$5</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">Executive_Dashboard!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -656,7 +620,7 @@
                   <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>400</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>800</c:v>
@@ -745,7 +709,7 @@
                   <c:v>90.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>72.64</c:v>
+                  <c:v>108.96000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>145.28</c:v>
@@ -923,7 +887,7 @@
                   <c:v>88.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>70.44</c:v>
+                  <c:v>106.76</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>143.08000000000001</c:v>
@@ -3892,7 +3856,7 @@
         <v>500</v>
       </c>
       <c r="G2" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H2" s="2">
         <v>800</v>
@@ -3922,8 +3886,8 @@
         <v>90.8</v>
       </c>
       <c r="G3" s="2">
-        <f>C3*4</f>
-        <v>72.64</v>
+        <f>C3*6</f>
+        <v>108.96000000000001</v>
       </c>
       <c r="H3" s="2">
         <f>C3*8</f>
@@ -3982,7 +3946,7 @@
       </c>
       <c r="G5" s="2">
         <f>G3-G4</f>
-        <v>70.44</v>
+        <v>106.76</v>
       </c>
       <c r="H5" s="2">
         <f>H3-H4</f>
@@ -4009,14 +3973,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f9ef682c-7912-4780-84f4-a971df966cba" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b405d1f-d10b-4093-82f9-1855360715f6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4221,21 +4183,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f9ef682c-7912-4780-84f4-a971df966cba" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b405d1f-d10b-4093-82f9-1855360715f6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0D1079-5B4B-49D4-ADDA-486E009CBEBA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20FF6A95-94CC-4354-9C77-CD818EDE354A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f9ef682c-7912-4780-84f4-a971df966cba"/>
-    <ds:schemaRef ds:uri="7b405d1f-d10b-4093-82f9-1855360715f6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4260,9 +4221,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20FF6A95-94CC-4354-9C77-CD818EDE354A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0D1079-5B4B-49D4-ADDA-486E009CBEBA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9ef682c-7912-4780-84f4-a971df966cba"/>
+    <ds:schemaRef ds:uri="7b405d1f-d10b-4093-82f9-1855360715f6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>